--- a/Outreach/partnr_leads_master.xlsx
+++ b/Outreach/partnr_leads_master.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deeky\OneDrive\Desktop\Partnr\Outreach\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B53589-41DD-4B10-8561-413B9981B329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="All Leads" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Kitwe" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Lusaka" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="All Leads" sheetId="1" r:id="rId1"/>
+    <sheet name="Kitwe" sheetId="2" r:id="rId2"/>
+    <sheet name="Lusaka" sheetId="3" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,1526 +41,1523 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="504">
   <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">African Mining Consultants (AMC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate / Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@amc-africa.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 211 108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://amc-africa.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Deal 🤝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwin Mukonka (GM) replied 24 Mar. Calls: 1 Apr &amp; 2 Apr 2026. Website concept in progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meltcast Engineering Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@meltcasteng.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6786244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.meltcasteng.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sent 📤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECB Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Law Firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ecb.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 227 536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ecblp.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S Lumba &amp; Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting Firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silaslumba@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6906073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://slumbaandco.godaddysites.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLB Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@hlb.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 6097962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hlb.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copperbelt Katanga Mining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@copperbeltkatangamining.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+243 991 762 231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://copperbeltkatangamining.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Contacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Techfields Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@techfields.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 221 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.techfields.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDALIFT CONSTRUCTION COMPANY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medaliftcompanylimited@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 4855869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://65c2a1d92807c.site123.me/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUMISE ENGINEERING LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@eumiseengineering.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 0651381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.eumiseengineering.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitwe Processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@kitweprocessing.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 225 643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://kitweprocessing.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repro Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@repro.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6950262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.repro.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICYPEED Logistics Kitwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@icypeed.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 9263927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://icypeed.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast Logistics Kitwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@fastlogisticscargo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 222 090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.fastlogisticscargo.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY Cargo Kitwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service@fycargo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 0580840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.fycargo.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercury Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enquiries@mercury.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.mercury.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cargo Management &amp; Logistics Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@cmlzambia.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6999227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.cml-ltd.co.uk/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Instrumentation Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering / Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kitwe@eml-eis.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 5228077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.eml-eis.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Shaw Property Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@AaronShawProperties.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 7931510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.aaronshawproperties.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weighgrid Company Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@weighgrid.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 7957820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://weighgrid.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAVS Equipment Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@kavsequipment.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6992542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kavsequipment.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint Environmental &amp; Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental / Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@blueprintecon.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 6963378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://blueprintecon.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blu Splash Engineering Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@blu-splash.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 6990036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://blu-splash.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KITWE GOLD DETECTOR ZAMBIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@hayatiprospectors.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 8583074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://hayatiprospectors.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G&amp;H Transport Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport / Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ghtransport.africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 4778343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.ghtransport.co.za/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 5336061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lusaka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndilila Associates Architects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin@ndililaarchitects.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 228 190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.ndililaarchitects.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;J Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business management consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@mjconsultants.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 0054386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mjconsultants.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opportune Time Business Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin@opportunetime.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6428370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.opportuneconsultants.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madinawala Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mechanical engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enquiries@madinawalaengineering.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 4284411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://madinawalaengineering.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydro-flow Apex Co.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@hydroflowapex.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://hydroflowapex.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rankin Engineering Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@rankinengineering.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 291 195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rankinengineering.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabulous Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabulousengineeringinfo@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 9064419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://fabulousengineering.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEHIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhCorprorate Chartered Accountants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact@whc.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 236 751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.whc.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iABC Associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kkaluba@iabc.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 1919350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.iabc.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AA Electronics Kalambo Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic parts supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@aaelectronicszm.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 222 666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.aaelectronicszm.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lilly Brown &amp; Associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Law firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@lilybrownassociates.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 9803204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lilybrownassociates.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrackMe Business Solutions Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logistics service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@trackme.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 8547219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.trackme.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duniya Healthcare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hello@duniyahealthcare.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 7256646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.duniyahealthcare.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">harrison and associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accountant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp@harrisonandassociates.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 7654599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://harrisonandassociates.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D Kalima &amp; Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@dkalima.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 4379093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dkalima.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gulf First Shipping and Logistics LTD - Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freight Forwarding Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@gulffirst.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 5384698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.gulffirst.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. Findlay &amp; Associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@dfindlaylaw.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6751257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://dfindlaylaw.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCK Chambers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infodesk@lck.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 257 003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://lck.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ellis &amp; Co - Advocates Attorneys and Notaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ellis.org.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 252 709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ellislegal.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wani &amp; Co Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@mediarychambers.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 7768594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.mediarychambers.com/wani-and-co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May and Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@mayandco.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 250 580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mayandco.law/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLM Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@slmlegal.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 258 994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.slmpractitioners.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Law Association of Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawyers association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@laz.org.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 254 401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.laz.org.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theotis Mutemi Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@tmlp.com.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 222 511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://theotismutemi.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPJ Electronics Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronics company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@thespj.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 0865631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.thespj.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freight and Passenger Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportation service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fps@freight.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 286 462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.freight.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCC Technologies (Pty) Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@dcctech.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 7261020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dcctech.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asian Medicos Enterprise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical supply store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filler@godaddy.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 233 857 ext. 222720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.asianmedicosenterprise.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPA Legal Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@jpalegal.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.jpalegal.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Designworx Studios Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Print shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@designworxstudios.net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 237 935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.designworxstudios.net/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appletech Business Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy equipment and solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appletechbusinesssolutions@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 2333053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://appletechbusinesssolutions.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zhengzhou unique industrial equipment co.,ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factory equipment supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@unique-cons.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+86 132 8384 3073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.uniquemacglobal.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aston AIR Car Hire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car rental agency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@astonairgroup.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 7500500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://astonairgroup.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INARA INVESTMENTS ZAMBIA LIMITED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@inarainvestments.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 7435735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.inarainvestments.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alick Suma health consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceutical company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hello@zambiadirectory.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 77 3832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.zambiadirectory.com/lusaka/manufacturing-industrial/alick-suma-health-consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heptagon Engineering LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar energy company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@theheptagon.co.za</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 8826988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.theheptagon.co.za/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tropical Products Zambia Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@tropicalint.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 7630000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.tropicalint.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORANGE PHARMA LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@orangepharmazm.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 6834918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orangepharmazm.co/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agro-Fuel Investments Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@agrofuelinvestments.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 288 836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://agrofuelinvestments.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajay Industrial Corporation Zambia Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irrigation equipment supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ajayindustrial.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 3924724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.ajayindustrial.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBS industries Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balajiagroltd@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 7944622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.balajiagroltd.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linkage International Shipping &amp; Forwarding Zambia since 1983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linkage@linkage.ae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 1164438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.linkageworldwide.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intergrity Cargo Pty Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@intergritycargo.co.za</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 7495277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.intergritycargo.co.za/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastlight Logistics Zambia Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courier service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@eastlightzambia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 7856565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.eastlight.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRA Express</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@braexpresszambia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 95 7113070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://braexpresszambia.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juba Transport SA (pty) Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trucking company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@jubatransport.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 2754535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.jubatransport.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forlan Logistics Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flcardealers@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 7929253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.forlanlogistics.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infix Logistics Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales@infixlogistics.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 4362195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://infixlogistics.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City Worx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity surveyor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin@cityworx.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 258 263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.cityworx.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corelink Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@corelink.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 3493849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.corelink.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insulated Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insulatedsystems@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 3766180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.insulatedsystemsltd.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zambia Transport and Logistics News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin@zambiatransportandlogistics.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 4118654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://zambiatransportandlogistics.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reeds Business Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daniel.katongo@reedsadvisory.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 96 8934750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.reedsbusinesssolutions.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRLeverage Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human resource consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hello@hrleveragezambia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 97 2848499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hrleveragezambia.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hilti - Nemchem Lusaka Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction equipment supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anneme@nemchem.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 76 0631904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hilti.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creative Aluminium &amp; Glass Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@creative-aluminium.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 846 277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.creative-aluminium.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muyatwa Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@muyatwalegal.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.muyatwalegal.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMW &amp; Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@amwlegal.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 237957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amw-legal.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musa Dudhia &amp; Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@musadudhia.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://aln.africa/our-offices/aln-zambia-musa-dudhia-co/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowmans – B&amp;M Legal Practitioners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info-zb@bowmanslaw.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 356638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bowmanslaw.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malisa and Partners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@malisaandpartners.law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.malisaandpartners.law/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chibesakunda &amp; Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mwelwa.chibesakunda@cco.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 366400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dlapiperafrica.com/en/zambia/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May &amp; Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@mayandco.law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGM Consulting Engineers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ngm@ngmzambia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 955781519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ngmzambia.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replied 💬</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLiONE Consulting Engineers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin@allioneconsulting.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.allioneconsulting.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMG Global Chartered Accountants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fridaynyambe@amgglobal.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 251159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actco Accountants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@actco.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 977 827272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baker Tilly Gwatidzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enquiries@bakertillygwatidzo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 269416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolands Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kelvinc@nolands.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 764 728388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://nolands.global/zambia/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@amazonassociates.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 955 766618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hill &amp; Delamain (Zambia) Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logistics@hdcargo.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 211 286480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hill-delamain.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Logistics Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@globalzm.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 977 476711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://globalzm.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow Logistics Solutions Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@flowlogisticszambia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://flowlogisticszambia.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercury Express Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 971 269390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concorde Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@concorde.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://concorde.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECMining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ecmining.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ecmining.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining Haulage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trucks@mininghaulage.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+260 212 314058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.mininghaulage.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Estates Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@centralestates.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.centralestates.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seeff Properties Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@seeff.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.seeff.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCA Properties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@bcaproperties.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://bcaproperties.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Properties Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@thehorizonproperties.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://thehorizonproperties.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primate Real Estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@primaterealestate.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.primaterealestate.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KSM Management Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@ksm.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ksm.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brilliance Executive Management Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR / management consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@bemconsult.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://bemconsult.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recruitment / HR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@talenthousepeople.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://talenthousepeople.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lift &amp; Shift Trucking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@liftandshifttrucking.co.zm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://liftandshifttrucking.co.zm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partnr Outreach — Lead Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-updates when statuses change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPELINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🤝  Active Deal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">💬  Replied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📤  Sent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📝  Draft Ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⬜  Not Contacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL LEADS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL TOUCHED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BY CITY</t>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Business Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>African Mining Consultants (AMC)</t>
+  </si>
+  <si>
+    <t>Corporate / Consulting</t>
+  </si>
+  <si>
+    <t>info@amc-africa.com</t>
+  </si>
+  <si>
+    <t>+260 212 211 108</t>
+  </si>
+  <si>
+    <t>http://amc-africa.com/</t>
+  </si>
+  <si>
+    <t>Kitwe</t>
+  </si>
+  <si>
+    <t>Active Deal 🤝</t>
+  </si>
+  <si>
+    <t>Edwin Mukonka (GM) replied 24 Mar. Calls: 1 Apr &amp; 2 Apr 2026. Website concept in progress.</t>
+  </si>
+  <si>
+    <t>Meltcast Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>info@meltcasteng.com</t>
+  </si>
+  <si>
+    <t>+260 96 6786244</t>
+  </si>
+  <si>
+    <t>http://www.meltcasteng.com/</t>
+  </si>
+  <si>
+    <t>Sent 📤</t>
+  </si>
+  <si>
+    <t>ECB Legal Practitioners</t>
+  </si>
+  <si>
+    <t>Law Firm</t>
+  </si>
+  <si>
+    <t>info@ecb.co.zm</t>
+  </si>
+  <si>
+    <t>+260 212 227 536</t>
+  </si>
+  <si>
+    <t>https://www.ecblp.com/</t>
+  </si>
+  <si>
+    <t>S Lumba &amp; Co</t>
+  </si>
+  <si>
+    <t>Accounting Firm</t>
+  </si>
+  <si>
+    <t>silaslumba@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 96 6906073</t>
+  </si>
+  <si>
+    <t>https://slumbaandco.godaddysites.com/</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>HLB Zambia</t>
+  </si>
+  <si>
+    <t>info@hlb.co.zm</t>
+  </si>
+  <si>
+    <t>+260 95 6097962</t>
+  </si>
+  <si>
+    <t>https://www.hlb.co.zm/</t>
+  </si>
+  <si>
+    <t>Copperbelt Katanga Mining</t>
+  </si>
+  <si>
+    <t>Mining Company</t>
+  </si>
+  <si>
+    <t>info@copperbeltkatangamining.com</t>
+  </si>
+  <si>
+    <t>+243 991 762 231</t>
+  </si>
+  <si>
+    <t>https://copperbeltkatangamining.com/</t>
+  </si>
+  <si>
+    <t>Not Contacted</t>
+  </si>
+  <si>
+    <t>Techfields Limited</t>
+  </si>
+  <si>
+    <t>Industrial Equipment</t>
+  </si>
+  <si>
+    <t>sales@techfields.co.zm</t>
+  </si>
+  <si>
+    <t>+260 212 221 300</t>
+  </si>
+  <si>
+    <t>http://www.techfields.co.zm/</t>
+  </si>
+  <si>
+    <t>MEDALIFT CONSTRUCTION COMPANY</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>medaliftcompanylimited@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 96 4855869</t>
+  </si>
+  <si>
+    <t>https://65c2a1d92807c.site123.me/</t>
+  </si>
+  <si>
+    <t>EUMISE ENGINEERING LTD</t>
+  </si>
+  <si>
+    <t>sales@eumiseengineering.com</t>
+  </si>
+  <si>
+    <t>+260 77 0651381</t>
+  </si>
+  <si>
+    <t>https://www.eumiseengineering.com/</t>
+  </si>
+  <si>
+    <t>Kitwe Processing</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>sales@kitweprocessing.com</t>
+  </si>
+  <si>
+    <t>+260 212 225 643</t>
+  </si>
+  <si>
+    <t>http://kitweprocessing.com/</t>
+  </si>
+  <si>
+    <t>Repro Limited</t>
+  </si>
+  <si>
+    <t>Office Equipment</t>
+  </si>
+  <si>
+    <t>info@repro.co.zm</t>
+  </si>
+  <si>
+    <t>+260 96 6950262</t>
+  </si>
+  <si>
+    <t>http://www.repro.co.zm/</t>
+  </si>
+  <si>
+    <t>ICYPEED Logistics Kitwe</t>
+  </si>
+  <si>
+    <t>Logistics</t>
+  </si>
+  <si>
+    <t>info@icypeed.com</t>
+  </si>
+  <si>
+    <t>+260 96 9263927</t>
+  </si>
+  <si>
+    <t>https://icypeed.com/</t>
+  </si>
+  <si>
+    <t>Fast Logistics Kitwe</t>
+  </si>
+  <si>
+    <t>info@fastlogisticscargo.com</t>
+  </si>
+  <si>
+    <t>+260 212 222 090</t>
+  </si>
+  <si>
+    <t>http://www.fastlogisticscargo.com/</t>
+  </si>
+  <si>
+    <t>FY Cargo Kitwe</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>service@fycargo.com</t>
+  </si>
+  <si>
+    <t>+260 76 0580840</t>
+  </si>
+  <si>
+    <t>http://www.fycargo.com/</t>
+  </si>
+  <si>
+    <t>Mercury Logistics</t>
+  </si>
+  <si>
+    <t>enquiries@mercury.co.zm</t>
+  </si>
+  <si>
+    <t>https://www.mercury.co.zm/</t>
+  </si>
+  <si>
+    <t>Cargo Management &amp; Logistics Zambia</t>
+  </si>
+  <si>
+    <t>info@cmlzambia.co.zm</t>
+  </si>
+  <si>
+    <t>+260 96 6999227</t>
+  </si>
+  <si>
+    <t>http://www.cml-ltd.co.uk/</t>
+  </si>
+  <si>
+    <t>Electrical Instrumentation Services LTD</t>
+  </si>
+  <si>
+    <t>Engineering / Equipment</t>
+  </si>
+  <si>
+    <t>kitwe@eml-eis.com</t>
+  </si>
+  <si>
+    <t>+260 95 5228077</t>
+  </si>
+  <si>
+    <t>http://www.eml-eis.com/</t>
+  </si>
+  <si>
+    <t>Aaron Shaw Property Consultants</t>
+  </si>
+  <si>
+    <t>Property Consulting</t>
+  </si>
+  <si>
+    <t>info@AaronShawProperties.com</t>
+  </si>
+  <si>
+    <t>+260 96 7931510</t>
+  </si>
+  <si>
+    <t>http://www.aaronshawproperties.com/</t>
+  </si>
+  <si>
+    <t>Weighgrid Company Limited</t>
+  </si>
+  <si>
+    <t>Equipment Supplier</t>
+  </si>
+  <si>
+    <t>sales@weighgrid.com</t>
+  </si>
+  <si>
+    <t>+260 97 7957820</t>
+  </si>
+  <si>
+    <t>https://weighgrid.com/</t>
+  </si>
+  <si>
+    <t>KAVS Equipment Ltd</t>
+  </si>
+  <si>
+    <t>Mining Equipment</t>
+  </si>
+  <si>
+    <t>info@kavsequipment.com</t>
+  </si>
+  <si>
+    <t>+260 96 6992542</t>
+  </si>
+  <si>
+    <t>https://www.kavsequipment.com/</t>
+  </si>
+  <si>
+    <t>Blueprint Environmental &amp; Construction</t>
+  </si>
+  <si>
+    <t>Environmental / Construction</t>
+  </si>
+  <si>
+    <t>info@blueprintecon.com</t>
+  </si>
+  <si>
+    <t>+260 95 6963378</t>
+  </si>
+  <si>
+    <t>http://blueprintecon.com/</t>
+  </si>
+  <si>
+    <t>Blu Splash Engineering Ltd</t>
+  </si>
+  <si>
+    <t>info@blu-splash.com</t>
+  </si>
+  <si>
+    <t>+260 76 6990036</t>
+  </si>
+  <si>
+    <t>https://blu-splash.com/</t>
+  </si>
+  <si>
+    <t>KITWE GOLD DETECTOR ZAMBIA</t>
+  </si>
+  <si>
+    <t>info@hayatiprospectors.com</t>
+  </si>
+  <si>
+    <t>+260 97 8583074</t>
+  </si>
+  <si>
+    <t>https://hayatiprospectors.com/</t>
+  </si>
+  <si>
+    <t>G&amp;H Transport Zambia</t>
+  </si>
+  <si>
+    <t>Transport / Logistics</t>
+  </si>
+  <si>
+    <t>info@ghtransport.africa</t>
+  </si>
+  <si>
+    <t>+260 76 4778343</t>
+  </si>
+  <si>
+    <t>http://www.ghtransport.co.za/</t>
+  </si>
+  <si>
+    <t>Accounting firm</t>
+  </si>
+  <si>
+    <t>+260 95 5336061</t>
+  </si>
+  <si>
+    <t>Lusaka</t>
+  </si>
+  <si>
+    <t>Ndilila Associates Architects</t>
+  </si>
+  <si>
+    <t>Architecture firm</t>
+  </si>
+  <si>
+    <t>admin@ndililaarchitects.com</t>
+  </si>
+  <si>
+    <t>+260 211 228 190</t>
+  </si>
+  <si>
+    <t>http://www.ndililaarchitects.com/</t>
+  </si>
+  <si>
+    <t>M&amp;J Zambia</t>
+  </si>
+  <si>
+    <t>Business management consultant</t>
+  </si>
+  <si>
+    <t>info@mjconsultants.co.zm</t>
+  </si>
+  <si>
+    <t>+260 95 0054386</t>
+  </si>
+  <si>
+    <t>https://mjconsultants.co.zm/</t>
+  </si>
+  <si>
+    <t>Opportune Time Business Consultants</t>
+  </si>
+  <si>
+    <t>Tax consultant</t>
+  </si>
+  <si>
+    <t>admin@opportunetime.com</t>
+  </si>
+  <si>
+    <t>+260 96 6428370</t>
+  </si>
+  <si>
+    <t>https://www.opportuneconsultants.com/</t>
+  </si>
+  <si>
+    <t>Madinawala Engineering</t>
+  </si>
+  <si>
+    <t>Mechanical engineer</t>
+  </si>
+  <si>
+    <t>enquiries@madinawalaengineering.com</t>
+  </si>
+  <si>
+    <t>+260 97 4284411</t>
+  </si>
+  <si>
+    <t>https://madinawalaengineering.com/</t>
+  </si>
+  <si>
+    <t>Hydro-flow Apex Co.</t>
+  </si>
+  <si>
+    <t>Consultant</t>
+  </si>
+  <si>
+    <t>info@hydroflowapex.com</t>
+  </si>
+  <si>
+    <t>https://hydroflowapex.com/</t>
+  </si>
+  <si>
+    <t>Rankin Engineering Consultants</t>
+  </si>
+  <si>
+    <t>Engineering consultant</t>
+  </si>
+  <si>
+    <t>info@rankinengineering.com</t>
+  </si>
+  <si>
+    <t>+260 211 291 195</t>
+  </si>
+  <si>
+    <t>https://www.rankinengineering.com/</t>
+  </si>
+  <si>
+    <t>Fabulous Engineering</t>
+  </si>
+  <si>
+    <t>Fabulousengineeringinfo@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 96 9064419</t>
+  </si>
+  <si>
+    <t>http://fabulousengineering.com/</t>
+  </si>
+  <si>
+    <t>BEHIND</t>
+  </si>
+  <si>
+    <t>WhCorprorate Chartered Accountants</t>
+  </si>
+  <si>
+    <t>contact@whc.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 236 751</t>
+  </si>
+  <si>
+    <t>http://www.whc.co.zm/</t>
+  </si>
+  <si>
+    <t>iABC Associates</t>
+  </si>
+  <si>
+    <t>Financial audit</t>
+  </si>
+  <si>
+    <t>kkaluba@iabc.co.zm</t>
+  </si>
+  <si>
+    <t>+260 76 1919350</t>
+  </si>
+  <si>
+    <t>http://www.iabc.co.zm/</t>
+  </si>
+  <si>
+    <t>AA Electronics Kalambo Road</t>
+  </si>
+  <si>
+    <t>Electronic parts supplier</t>
+  </si>
+  <si>
+    <t>sales@aaelectronicszm.com</t>
+  </si>
+  <si>
+    <t>+260 211 222 666</t>
+  </si>
+  <si>
+    <t>http://www.aaelectronicszm.com/</t>
+  </si>
+  <si>
+    <t>Lilly Brown &amp; Associates</t>
+  </si>
+  <si>
+    <t>Law firm</t>
+  </si>
+  <si>
+    <t>info@lilybrownassociates.com</t>
+  </si>
+  <si>
+    <t>+260 76 9803204</t>
+  </si>
+  <si>
+    <t>https://www.lilybrownassociates.com/</t>
+  </si>
+  <si>
+    <t>TrackMe Business Solutions Limited</t>
+  </si>
+  <si>
+    <t>Logistics service</t>
+  </si>
+  <si>
+    <t>info@trackme.co.zm</t>
+  </si>
+  <si>
+    <t>+260 76 8547219</t>
+  </si>
+  <si>
+    <t>https://www.trackme.co.zm/</t>
+  </si>
+  <si>
+    <t>Duniya Healthcare</t>
+  </si>
+  <si>
+    <t>hello@duniyahealthcare.com</t>
+  </si>
+  <si>
+    <t>+260 77 7256646</t>
+  </si>
+  <si>
+    <t>https://www.duniyahealthcare.com/</t>
+  </si>
+  <si>
+    <t>harrison and associates</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>mp@harrisonandassociates.com</t>
+  </si>
+  <si>
+    <t>+260 97 7654599</t>
+  </si>
+  <si>
+    <t>http://harrisonandassociates.com/</t>
+  </si>
+  <si>
+    <t>D Kalima &amp; Company</t>
+  </si>
+  <si>
+    <t>info@dkalima.com</t>
+  </si>
+  <si>
+    <t>+260 97 4379093</t>
+  </si>
+  <si>
+    <t>https://www.dkalima.com/</t>
+  </si>
+  <si>
+    <t>Gulf First Shipping and Logistics LTD - Zambia</t>
+  </si>
+  <si>
+    <t>Freight Forwarding Service</t>
+  </si>
+  <si>
+    <t>info@gulffirst.com</t>
+  </si>
+  <si>
+    <t>+260 96 5384698</t>
+  </si>
+  <si>
+    <t>https://www.gulffirst.com/</t>
+  </si>
+  <si>
+    <t>D. Findlay &amp; Associates</t>
+  </si>
+  <si>
+    <t>Corporate office</t>
+  </si>
+  <si>
+    <t>info@dfindlaylaw.com</t>
+  </si>
+  <si>
+    <t>+260 96 6751257</t>
+  </si>
+  <si>
+    <t>https://dfindlaylaw.com/</t>
+  </si>
+  <si>
+    <t>LCK Chambers</t>
+  </si>
+  <si>
+    <t>infodesk@lck.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 257 003</t>
+  </si>
+  <si>
+    <t>https://lck.co.zm/</t>
+  </si>
+  <si>
+    <t>Ellis &amp; Co - Advocates Attorneys and Notaries</t>
+  </si>
+  <si>
+    <t>info@ellis.org.zm</t>
+  </si>
+  <si>
+    <t>+260 211 252 709</t>
+  </si>
+  <si>
+    <t>https://ellislegal.co.zm/</t>
+  </si>
+  <si>
+    <t>Wani &amp; Co Legal Practitioners</t>
+  </si>
+  <si>
+    <t>info@mediarychambers.com</t>
+  </si>
+  <si>
+    <t>+260 77 7768594</t>
+  </si>
+  <si>
+    <t>https://www.mediarychambers.com/wani-and-co</t>
+  </si>
+  <si>
+    <t>May and Company</t>
+  </si>
+  <si>
+    <t>Legal services</t>
+  </si>
+  <si>
+    <t>info@mayandco.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 250 580</t>
+  </si>
+  <si>
+    <t>https://mayandco.law/</t>
+  </si>
+  <si>
+    <t>SLM Legal Practitioners</t>
+  </si>
+  <si>
+    <t>info@slmlegal.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 258 994</t>
+  </si>
+  <si>
+    <t>https://www.slmpractitioners.com/</t>
+  </si>
+  <si>
+    <t>Law Association of Zambia</t>
+  </si>
+  <si>
+    <t>Lawyers association</t>
+  </si>
+  <si>
+    <t>info@laz.org.zm</t>
+  </si>
+  <si>
+    <t>+260 211 254 401</t>
+  </si>
+  <si>
+    <t>http://www.laz.org.zm/</t>
+  </si>
+  <si>
+    <t>Theotis Mutemi Legal Practitioners</t>
+  </si>
+  <si>
+    <t>info@tmlp.com.zm</t>
+  </si>
+  <si>
+    <t>+260 211 222 511</t>
+  </si>
+  <si>
+    <t>https://theotismutemi.com/</t>
+  </si>
+  <si>
+    <t>SPJ Electronics Zambia</t>
+  </si>
+  <si>
+    <t>Electronics company</t>
+  </si>
+  <si>
+    <t>info@thespj.com</t>
+  </si>
+  <si>
+    <t>+260 77 0865631</t>
+  </si>
+  <si>
+    <t>https://www.thespj.com/</t>
+  </si>
+  <si>
+    <t>Freight and Passenger Services LTD</t>
+  </si>
+  <si>
+    <t>Transportation service</t>
+  </si>
+  <si>
+    <t>fps@freight.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 286 462</t>
+  </si>
+  <si>
+    <t>https://www.freight.co.zm/</t>
+  </si>
+  <si>
+    <t>DCC Technologies (Pty) Ltd</t>
+  </si>
+  <si>
+    <t>Distribution service</t>
+  </si>
+  <si>
+    <t>info@dcctech.com</t>
+  </si>
+  <si>
+    <t>+260 97 7261020</t>
+  </si>
+  <si>
+    <t>https://www.dcctech.com/</t>
+  </si>
+  <si>
+    <t>Asian Medicos Enterprise</t>
+  </si>
+  <si>
+    <t>Medical supply store</t>
+  </si>
+  <si>
+    <t>filler@godaddy.com</t>
+  </si>
+  <si>
+    <t>+260 211 233 857 ext. 222720</t>
+  </si>
+  <si>
+    <t>http://www.asianmedicosenterprise.com/</t>
+  </si>
+  <si>
+    <t>JPA Legal Zambia</t>
+  </si>
+  <si>
+    <t>info@jpalegal.com</t>
+  </si>
+  <si>
+    <t>https://www.jpalegal.com/</t>
+  </si>
+  <si>
+    <t>Designworx Studios Ltd</t>
+  </si>
+  <si>
+    <t>Print shop</t>
+  </si>
+  <si>
+    <t>info@designworxstudios.net</t>
+  </si>
+  <si>
+    <t>+260 211 237 935</t>
+  </si>
+  <si>
+    <t>http://www.designworxstudios.net/</t>
+  </si>
+  <si>
+    <t>Appletech Business Solutions</t>
+  </si>
+  <si>
+    <t>Energy equipment and solutions</t>
+  </si>
+  <si>
+    <t>appletechbusinesssolutions@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 97 2333053</t>
+  </si>
+  <si>
+    <t>https://appletechbusinesssolutions.org/</t>
+  </si>
+  <si>
+    <t>zhengzhou unique industrial equipment co.,ltd</t>
+  </si>
+  <si>
+    <t>Factory equipment supplier</t>
+  </si>
+  <si>
+    <t>sales@unique-cons.com</t>
+  </si>
+  <si>
+    <t>+86 132 8384 3073</t>
+  </si>
+  <si>
+    <t>https://www.uniquemacglobal.com/</t>
+  </si>
+  <si>
+    <t>Aston AIR Car Hire</t>
+  </si>
+  <si>
+    <t>Car rental agency</t>
+  </si>
+  <si>
+    <t>info@astonairgroup.co.zm</t>
+  </si>
+  <si>
+    <t>+260 97 7500500</t>
+  </si>
+  <si>
+    <t>https://astonairgroup.co.zm/</t>
+  </si>
+  <si>
+    <t>INARA INVESTMENTS ZAMBIA LIMITED</t>
+  </si>
+  <si>
+    <t>info@inarainvestments.com</t>
+  </si>
+  <si>
+    <t>+260 77 7435735</t>
+  </si>
+  <si>
+    <t>http://www.inarainvestments.com/</t>
+  </si>
+  <si>
+    <t>Alick Suma health consultant</t>
+  </si>
+  <si>
+    <t>Pharmaceutical company</t>
+  </si>
+  <si>
+    <t>hello@zambiadirectory.com</t>
+  </si>
+  <si>
+    <t>+260 77 3832733</t>
+  </si>
+  <si>
+    <t>https://www.zambiadirectory.com/lusaka/manufacturing-industrial/alick-suma-health-consultant</t>
+  </si>
+  <si>
+    <t>The Heptagon Engineering LTD</t>
+  </si>
+  <si>
+    <t>Solar energy company</t>
+  </si>
+  <si>
+    <t>sales@theheptagon.co.za</t>
+  </si>
+  <si>
+    <t>+260 97 8826988</t>
+  </si>
+  <si>
+    <t>http://www.theheptagon.co.za/</t>
+  </si>
+  <si>
+    <t>Tropical Products Zambia Limited</t>
+  </si>
+  <si>
+    <t>sales@tropicalint.com</t>
+  </si>
+  <si>
+    <t>+260 96 7630000</t>
+  </si>
+  <si>
+    <t>http://www.tropicalint.com/</t>
+  </si>
+  <si>
+    <t>ORANGE PHARMA LTD</t>
+  </si>
+  <si>
+    <t>info@orangepharmazm.co</t>
+  </si>
+  <si>
+    <t>+260 96 6834918</t>
+  </si>
+  <si>
+    <t>https://orangepharmazm.co/</t>
+  </si>
+  <si>
+    <t>Agro-Fuel Investments Ltd.</t>
+  </si>
+  <si>
+    <t>info@agrofuelinvestments.com</t>
+  </si>
+  <si>
+    <t>+260 211 288 836</t>
+  </si>
+  <si>
+    <t>http://agrofuelinvestments.com/</t>
+  </si>
+  <si>
+    <t>Ajay Industrial Corporation Zambia Limited</t>
+  </si>
+  <si>
+    <t>Irrigation equipment supplier</t>
+  </si>
+  <si>
+    <t>info@ajayindustrial.com</t>
+  </si>
+  <si>
+    <t>+260 97 3924724</t>
+  </si>
+  <si>
+    <t>http://www.ajayindustrial.com/</t>
+  </si>
+  <si>
+    <t>MBS industries Ltd</t>
+  </si>
+  <si>
+    <t>Balajiagroltd@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 95 7944622</t>
+  </si>
+  <si>
+    <t>http://www.balajiagroltd.com/</t>
+  </si>
+  <si>
+    <t>Linkage International Shipping &amp; Forwarding Zambia since 1983</t>
+  </si>
+  <si>
+    <t>Shipping service</t>
+  </si>
+  <si>
+    <t>linkage@linkage.ae</t>
+  </si>
+  <si>
+    <t>+260 97 1164438</t>
+  </si>
+  <si>
+    <t>http://www.linkageworldwide.com/</t>
+  </si>
+  <si>
+    <t>Intergrity Cargo Pty Ltd</t>
+  </si>
+  <si>
+    <t>info@intergritycargo.co.za</t>
+  </si>
+  <si>
+    <t>+260 96 7495277</t>
+  </si>
+  <si>
+    <t>https://www.intergritycargo.co.za/</t>
+  </si>
+  <si>
+    <t>Eastlight Logistics Zambia Ltd</t>
+  </si>
+  <si>
+    <t>Courier service</t>
+  </si>
+  <si>
+    <t>info@eastlightzambia.com</t>
+  </si>
+  <si>
+    <t>+260 97 7856565</t>
+  </si>
+  <si>
+    <t>http://www.eastlight.org/</t>
+  </si>
+  <si>
+    <t>BRA Express</t>
+  </si>
+  <si>
+    <t>info@braexpresszambia.com</t>
+  </si>
+  <si>
+    <t>+260 95 7113070</t>
+  </si>
+  <si>
+    <t>https://braexpresszambia.com/</t>
+  </si>
+  <si>
+    <t>Juba Transport SA (pty) Ltd</t>
+  </si>
+  <si>
+    <t>Trucking company</t>
+  </si>
+  <si>
+    <t>info@jubatransport.co.zm</t>
+  </si>
+  <si>
+    <t>+260 97 2754535</t>
+  </si>
+  <si>
+    <t>http://www.jubatransport.co.zm/</t>
+  </si>
+  <si>
+    <t>Forlan Logistics Limited</t>
+  </si>
+  <si>
+    <t>flcardealers@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 96 7929253</t>
+  </si>
+  <si>
+    <t>https://www.forlanlogistics.com/</t>
+  </si>
+  <si>
+    <t>Infix Logistics Zambia</t>
+  </si>
+  <si>
+    <t>sales@infixlogistics.com</t>
+  </si>
+  <si>
+    <t>+260 97 4362195</t>
+  </si>
+  <si>
+    <t>https://infixlogistics.com/</t>
+  </si>
+  <si>
+    <t>City Worx</t>
+  </si>
+  <si>
+    <t>Quantity surveyor</t>
+  </si>
+  <si>
+    <t>admin@cityworx.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 258 263</t>
+  </si>
+  <si>
+    <t>http://www.cityworx.co.zm/</t>
+  </si>
+  <si>
+    <t>Corelink Consulting</t>
+  </si>
+  <si>
+    <t>Information services</t>
+  </si>
+  <si>
+    <t>info@corelink.co.zm</t>
+  </si>
+  <si>
+    <t>+260 96 3493849</t>
+  </si>
+  <si>
+    <t>https://www.corelink.co.zm/</t>
+  </si>
+  <si>
+    <t>Insulated Systems</t>
+  </si>
+  <si>
+    <t>Construction company</t>
+  </si>
+  <si>
+    <t>insulatedsystems@gmail.com</t>
+  </si>
+  <si>
+    <t>+260 96 3766180</t>
+  </si>
+  <si>
+    <t>http://www.insulatedsystemsltd.com/</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Zambia Transport and Logistics News</t>
+  </si>
+  <si>
+    <t>admin@zambiatransportandlogistics.com</t>
+  </si>
+  <si>
+    <t>+260 96 4118654</t>
+  </si>
+  <si>
+    <t>https://zambiatransportandlogistics.com/</t>
+  </si>
+  <si>
+    <t>Reeds Business Solutions</t>
+  </si>
+  <si>
+    <t>daniel.katongo@reedsadvisory.com</t>
+  </si>
+  <si>
+    <t>+260 96 8934750</t>
+  </si>
+  <si>
+    <t>http://www.reedsbusinesssolutions.com/</t>
+  </si>
+  <si>
+    <t>HRLeverage Zambia</t>
+  </si>
+  <si>
+    <t>Human resource consulting</t>
+  </si>
+  <si>
+    <t>hello@hrleveragezambia.com</t>
+  </si>
+  <si>
+    <t>+260 97 2848499</t>
+  </si>
+  <si>
+    <t>https://www.hrleveragezambia.com/</t>
+  </si>
+  <si>
+    <t>Hilti - Nemchem Lusaka Office</t>
+  </si>
+  <si>
+    <t>Construction equipment supplier</t>
+  </si>
+  <si>
+    <t>anneme@nemchem.co.zm</t>
+  </si>
+  <si>
+    <t>+260 76 0631904</t>
+  </si>
+  <si>
+    <t>https://www.hilti.co.zm/</t>
+  </si>
+  <si>
+    <t>Creative Aluminium &amp; Glass Limited</t>
+  </si>
+  <si>
+    <t>info@creative-aluminium.com</t>
+  </si>
+  <si>
+    <t>+260 211 846 277</t>
+  </si>
+  <si>
+    <t>http://www.creative-aluminium.com/</t>
+  </si>
+  <si>
+    <t>Muyatwa Legal Practitioners</t>
+  </si>
+  <si>
+    <t>info@muyatwalegal.com</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>https://www.muyatwalegal.com/</t>
+  </si>
+  <si>
+    <t>AMW &amp; Co</t>
+  </si>
+  <si>
+    <t>info@amwlegal.com</t>
+  </si>
+  <si>
+    <t>+260 211 237957</t>
+  </si>
+  <si>
+    <t>https://www.amw-legal.com/</t>
+  </si>
+  <si>
+    <t>Musa Dudhia &amp; Co</t>
+  </si>
+  <si>
+    <t>info@musadudhia.co.zm</t>
+  </si>
+  <si>
+    <t>https://aln.africa/our-offices/aln-zambia-musa-dudhia-co/</t>
+  </si>
+  <si>
+    <t>Bowmans – B&amp;M Legal Practitioners</t>
+  </si>
+  <si>
+    <t>info-zb@bowmanslaw.com</t>
+  </si>
+  <si>
+    <t>+260 211 356638</t>
+  </si>
+  <si>
+    <t>https://www.bowmanslaw.com/</t>
+  </si>
+  <si>
+    <t>Malisa and Partners</t>
+  </si>
+  <si>
+    <t>info@malisaandpartners.law</t>
+  </si>
+  <si>
+    <t>https://www.malisaandpartners.law/</t>
+  </si>
+  <si>
+    <t>Chibesakunda &amp; Co</t>
+  </si>
+  <si>
+    <t>mwelwa.chibesakunda@cco.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 366400</t>
+  </si>
+  <si>
+    <t>https://www.dlapiperafrica.com/en/zambia/</t>
+  </si>
+  <si>
+    <t>May &amp; Co</t>
+  </si>
+  <si>
+    <t>info@mayandco.law</t>
+  </si>
+  <si>
+    <t>NGM Consulting Engineers</t>
+  </si>
+  <si>
+    <t>ngm@ngmzambia.com</t>
+  </si>
+  <si>
+    <t>+260 955781519</t>
+  </si>
+  <si>
+    <t>https://ngmzambia.com/</t>
+  </si>
+  <si>
+    <t>Replied 💬</t>
+  </si>
+  <si>
+    <t>ALLiONE Consulting Engineers</t>
+  </si>
+  <si>
+    <t>admin@allioneconsulting.com</t>
+  </si>
+  <si>
+    <t>https://www.allioneconsulting.com/</t>
+  </si>
+  <si>
+    <t>AMG Global Chartered Accountants</t>
+  </si>
+  <si>
+    <t>fridaynyambe@amgglobal.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 251159</t>
+  </si>
+  <si>
+    <t>Actco Accountants</t>
+  </si>
+  <si>
+    <t>info@actco.co.zm</t>
+  </si>
+  <si>
+    <t>+260 977 827272</t>
+  </si>
+  <si>
+    <t>Baker Tilly Gwatidzo</t>
+  </si>
+  <si>
+    <t>enquiries@bakertillygwatidzo.com</t>
+  </si>
+  <si>
+    <t>+260 211 269416</t>
+  </si>
+  <si>
+    <t>Nolands Zambia</t>
+  </si>
+  <si>
+    <t>kelvinc@nolands.co.zm</t>
+  </si>
+  <si>
+    <t>+260 764 728388</t>
+  </si>
+  <si>
+    <t>https://nolands.global/zambia/</t>
+  </si>
+  <si>
+    <t>Amazon Associates</t>
+  </si>
+  <si>
+    <t>info@amazonassociates.co.zm</t>
+  </si>
+  <si>
+    <t>+260 955 766618</t>
+  </si>
+  <si>
+    <t>Hill &amp; Delamain (Zambia) Ltd</t>
+  </si>
+  <si>
+    <t>logistics@hdcargo.co.zm</t>
+  </si>
+  <si>
+    <t>+260 211 286480</t>
+  </si>
+  <si>
+    <t>https://www.hill-delamain.co.zm/</t>
+  </si>
+  <si>
+    <t>Global Logistics Limited</t>
+  </si>
+  <si>
+    <t>info@globalzm.com</t>
+  </si>
+  <si>
+    <t>+260 977 476711</t>
+  </si>
+  <si>
+    <t>https://globalzm.com/</t>
+  </si>
+  <si>
+    <t>Flow Logistics Solutions Limited</t>
+  </si>
+  <si>
+    <t>info@flowlogisticszambia.com</t>
+  </si>
+  <si>
+    <t>https://flowlogisticszambia.com/</t>
+  </si>
+  <si>
+    <t>Mercury Express Logistics</t>
+  </si>
+  <si>
+    <t>+260 971 269390</t>
+  </si>
+  <si>
+    <t>Concorde Construction</t>
+  </si>
+  <si>
+    <t>info@concorde.co.zm</t>
+  </si>
+  <si>
+    <t>https://concorde.co.zm/</t>
+  </si>
+  <si>
+    <t>ECMining</t>
+  </si>
+  <si>
+    <t>Mining services</t>
+  </si>
+  <si>
+    <t>info@ecmining.com</t>
+  </si>
+  <si>
+    <t>https://ecmining.com/</t>
+  </si>
+  <si>
+    <t>Mining Haulage</t>
+  </si>
+  <si>
+    <t>Mining transport</t>
+  </si>
+  <si>
+    <t>trucks@mininghaulage.co.zm</t>
+  </si>
+  <si>
+    <t>+260 212 314058</t>
+  </si>
+  <si>
+    <t>https://www.mininghaulage.co.zm/</t>
+  </si>
+  <si>
+    <t>Central Estates Zambia</t>
+  </si>
+  <si>
+    <t>Real estate</t>
+  </si>
+  <si>
+    <t>info@centralestates.org</t>
+  </si>
+  <si>
+    <t>https://www.centralestates.org/</t>
+  </si>
+  <si>
+    <t>Seeff Properties Zambia</t>
+  </si>
+  <si>
+    <t>info@seeff.co.zm</t>
+  </si>
+  <si>
+    <t>https://www.seeff.co.zm/</t>
+  </si>
+  <si>
+    <t>BCA Properties</t>
+  </si>
+  <si>
+    <t>info@bcaproperties.com</t>
+  </si>
+  <si>
+    <t>https://bcaproperties.com/</t>
+  </si>
+  <si>
+    <t>Horizon Properties Limited</t>
+  </si>
+  <si>
+    <t>info@thehorizonproperties.com</t>
+  </si>
+  <si>
+    <t>https://thehorizonproperties.com/</t>
+  </si>
+  <si>
+    <t>Primate Real Estate</t>
+  </si>
+  <si>
+    <t>info@primaterealestate.com</t>
+  </si>
+  <si>
+    <t>https://www.primaterealestate.com/</t>
+  </si>
+  <si>
+    <t>KSM Management Consultants</t>
+  </si>
+  <si>
+    <t>HR consulting</t>
+  </si>
+  <si>
+    <t>info@ksm.co.zm</t>
+  </si>
+  <si>
+    <t>https://ksm.co.zm/</t>
+  </si>
+  <si>
+    <t>Brilliance Executive Management Consultants</t>
+  </si>
+  <si>
+    <t>HR / management consulting</t>
+  </si>
+  <si>
+    <t>info@bemconsult.com</t>
+  </si>
+  <si>
+    <t>https://bemconsult.com/</t>
+  </si>
+  <si>
+    <t>Talent House</t>
+  </si>
+  <si>
+    <t>Recruitment / HR</t>
+  </si>
+  <si>
+    <t>info@talenthousepeople.com</t>
+  </si>
+  <si>
+    <t>https://talenthousepeople.com/</t>
+  </si>
+  <si>
+    <t>Lift &amp; Shift Trucking</t>
+  </si>
+  <si>
+    <t>info@liftandshifttrucking.co.zm</t>
+  </si>
+  <si>
+    <t>https://liftandshifttrucking.co.zm/</t>
+  </si>
+  <si>
+    <t>Partnr Outreach — Lead Tracker</t>
+  </si>
+  <si>
+    <t>Auto-updates when statuses change</t>
+  </si>
+  <si>
+    <t>PIPELINE</t>
+  </si>
+  <si>
+    <t>🤝  Active Deal</t>
+  </si>
+  <si>
+    <t>💬  Replied</t>
+  </si>
+  <si>
+    <t>📤  Sent</t>
+  </si>
+  <si>
+    <t>📝  Draft Ready</t>
+  </si>
+  <si>
+    <t>⬜  Not Contacted</t>
+  </si>
+  <si>
+    <t>TOTAL LEADS</t>
+  </si>
+  <si>
+    <t>TOTAL TOUCHED</t>
+  </si>
+  <si>
+    <t>BY CITY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1553,100 +1566,82 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF2E75B6"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Aptos"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1A7A1A"/>
       <name val="Aptos"/>
-      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1707,14 +1702,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -1729,7 +1724,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -1745,125 +1740,81 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1922,13 +1873,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1A5276"/>
       <rgbColor rgb="FF1F2937"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1970,12 +1937,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2004,7 +1971,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2025,7 +1992,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2076,7 +2043,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2094,34 +2061,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J112"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,8 +2119,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2175,7 +2141,7 @@
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>4.2</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -2185,8 +2151,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -2207,7 +2173,7 @@
       <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="4">
         <v>4.5</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -2215,8 +2181,8 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2237,16 +2203,16 @@
       <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>4.6</v>
+      <c r="H4" s="2">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -2275,8 +2241,8 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2305,8 +2271,8 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -2327,7 +2293,7 @@
       <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="4">
         <v>4.2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -2335,8 +2301,8 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2357,7 +2323,7 @@
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="2">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -2365,8 +2331,8 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -2375,7 +2341,7 @@
       <c r="C9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -2395,8 +2361,8 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2411,13 +2377,13 @@
       <c r="E10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="22" t="s">
         <v>58</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2">
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -2425,8 +2391,8 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -2447,16 +2413,16 @@
       <c r="G11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>4.1</v>
+      <c r="H11" s="4">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2477,7 +2443,7 @@
       <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="2">
         <v>3.5</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -2485,8 +2451,8 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -2507,7 +2473,7 @@
       <c r="G13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="4">
         <v>4</v>
       </c>
       <c r="I13" s="5" t="s">
@@ -2515,8 +2481,8 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2537,7 +2503,7 @@
       <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="2">
         <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -2545,8 +2511,8 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -2567,7 +2533,7 @@
       <c r="G15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="4">
         <v>3.9</v>
       </c>
       <c r="I15" s="5" t="s">
@@ -2575,8 +2541,8 @@
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2595,7 +2561,7 @@
       <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="2">
         <v>4.5</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -2603,8 +2569,8 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -2625,7 +2591,7 @@
       <c r="G17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="4">
         <v>4.5</v>
       </c>
       <c r="I17" s="5" t="s">
@@ -2633,8 +2599,8 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2655,7 +2621,7 @@
       <c r="G18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="2">
         <v>4.7</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -2663,8 +2629,8 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -2693,8 +2659,8 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2723,8 +2689,8 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -2745,7 +2711,7 @@
       <c r="G21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="4">
         <v>4.7</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -2753,8 +2719,8 @@
       </c>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2775,7 +2741,7 @@
       <c r="G22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="2">
         <v>4</v>
       </c>
       <c r="I22" s="3" t="s">
@@ -2783,8 +2749,8 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -2805,7 +2771,7 @@
       <c r="G23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="4">
         <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -2813,8 +2779,8 @@
       </c>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2843,8 +2809,8 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -2865,7 +2831,7 @@
       <c r="G25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4">
         <v>4.8</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -2873,8 +2839,8 @@
       </c>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -2895,7 +2861,7 @@
       <c r="G26" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="2">
         <v>4.3</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -2903,8 +2869,8 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -2925,7 +2891,7 @@
       <c r="G27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="4">
         <v>3.9</v>
       </c>
       <c r="I27" s="5" t="s">
@@ -2933,8 +2899,8 @@
       </c>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -2955,7 +2921,7 @@
       <c r="G28" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="2">
         <v>4.7</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -2963,8 +2929,8 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -2985,16 +2951,16 @@
       <c r="G29" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>4.9</v>
+      <c r="H29" s="4">
+        <v>4.9000000000000004</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -3015,16 +2981,16 @@
       <c r="G30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>4.4</v>
+      <c r="H30" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -3051,8 +3017,8 @@
       </c>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -3073,7 +3039,7 @@
       <c r="G32" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="2">
         <v>4.5</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -3081,8 +3047,8 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -3103,7 +3069,7 @@
       <c r="G33" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="4">
         <v>4.8</v>
       </c>
       <c r="I33" s="5" t="s">
@@ -3111,8 +3077,8 @@
       </c>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -3133,7 +3099,7 @@
       <c r="G34" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="2">
         <v>5</v>
       </c>
       <c r="I34" s="3" t="s">
@@ -3141,8 +3107,8 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -3171,8 +3137,8 @@
       </c>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -3193,16 +3159,16 @@
       <c r="G36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>4.1</v>
+      <c r="H36" s="2">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -3223,7 +3189,7 @@
       <c r="G37" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="4">
         <v>5</v>
       </c>
       <c r="I37" s="5" t="s">
@@ -3231,8 +3197,8 @@
       </c>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -3253,7 +3219,7 @@
       <c r="G38" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="2">
         <v>4.3</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -3261,8 +3227,8 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -3291,8 +3257,8 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -3313,7 +3279,7 @@
       <c r="G40" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="2">
         <v>5</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -3321,8 +3287,8 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -3351,8 +3317,8 @@
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -3381,8 +3347,8 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
@@ -3403,7 +3369,7 @@
       <c r="G43" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="4">
         <v>4.5</v>
       </c>
       <c r="I43" s="5" t="s">
@@ -3411,8 +3377,8 @@
       </c>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -3433,7 +3399,7 @@
       <c r="G44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="2">
         <v>5</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -3441,8 +3407,8 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -3463,7 +3429,7 @@
       <c r="G45" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="4">
         <v>4.5</v>
       </c>
       <c r="I45" s="5" t="s">
@@ -3471,8 +3437,8 @@
       </c>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -3501,8 +3467,8 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
@@ -3523,7 +3489,7 @@
       <c r="G47" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="4">
         <v>5</v>
       </c>
       <c r="I47" s="5" t="s">
@@ -3531,8 +3497,8 @@
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -3553,7 +3519,7 @@
       <c r="G48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="2">
         <v>5</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -3561,8 +3527,8 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
@@ -3583,7 +3549,7 @@
       <c r="G49" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="4">
         <v>4.2</v>
       </c>
       <c r="I49" s="5" t="s">
@@ -3591,8 +3557,8 @@
       </c>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -3613,7 +3579,7 @@
       <c r="G50" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="2">
         <v>4.2</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -3621,8 +3587,8 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
@@ -3643,16 +3609,16 @@
       <c r="G51" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H51" s="4" t="n">
-        <v>4.6</v>
+      <c r="H51" s="4">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J51" s="5"/>
     </row>
-    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -3673,16 +3639,16 @@
       <c r="G52" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H52" s="2" t="n">
-        <v>4.1</v>
+      <c r="H52" s="2">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
@@ -3711,8 +3677,8 @@
       </c>
       <c r="J53" s="5"/>
     </row>
-    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -3733,7 +3699,7 @@
       <c r="G54" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="2">
         <v>4.2</v>
       </c>
       <c r="I54" s="3" t="s">
@@ -3741,8 +3707,8 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
@@ -3769,8 +3735,8 @@
       </c>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -3791,7 +3757,7 @@
       <c r="G56" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="2">
         <v>4.5</v>
       </c>
       <c r="I56" s="3" t="s">
@@ -3799,8 +3765,8 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
@@ -3821,7 +3787,7 @@
       <c r="G57" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="4">
         <v>5</v>
       </c>
       <c r="I57" s="5" t="s">
@@ -3829,8 +3795,8 @@
       </c>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3859,8 +3825,8 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
+    <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
@@ -3881,7 +3847,7 @@
       <c r="G59" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="4">
         <v>5</v>
       </c>
       <c r="I59" s="5" t="s">
@@ -3889,8 +3855,8 @@
       </c>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3911,16 +3877,16 @@
       <c r="G60" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H60" s="2" t="n">
-        <v>4.6</v>
+      <c r="H60" s="2">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
+    <row r="61" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
@@ -3941,7 +3907,7 @@
       <c r="G61" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="4">
         <v>4.7</v>
       </c>
       <c r="I61" s="5" t="s">
@@ -3949,8 +3915,8 @@
       </c>
       <c r="J61" s="5"/>
     </row>
-    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3971,7 +3937,7 @@
       <c r="G62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="2">
         <v>5</v>
       </c>
       <c r="I62" s="3" t="s">
@@ -3979,8 +3945,8 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
+    <row r="63" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
@@ -4001,7 +3967,7 @@
       <c r="G63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="4">
         <v>4.5</v>
       </c>
       <c r="I63" s="5" t="s">
@@ -4009,8 +3975,8 @@
       </c>
       <c r="J63" s="5"/>
     </row>
-    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -4031,7 +3997,7 @@
       <c r="G64" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="2">
         <v>5</v>
       </c>
       <c r="I64" s="3" t="s">
@@ -4039,8 +4005,8 @@
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
+    <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
@@ -4061,7 +4027,7 @@
       <c r="G65" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="4">
         <v>4</v>
       </c>
       <c r="I65" s="5" t="s">
@@ -4069,8 +4035,8 @@
       </c>
       <c r="J65" s="5"/>
     </row>
-    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -4091,7 +4057,7 @@
       <c r="G66" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="2">
         <v>4.8</v>
       </c>
       <c r="I66" s="3" t="s">
@@ -4099,8 +4065,8 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
+    <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
@@ -4121,7 +4087,7 @@
       <c r="G67" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="4">
         <v>5</v>
       </c>
       <c r="I67" s="5" t="s">
@@ -4129,8 +4095,8 @@
       </c>
       <c r="J67" s="5"/>
     </row>
-    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -4151,16 +4117,16 @@
       <c r="G68" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H68" s="2" t="n">
-        <v>4.4</v>
+      <c r="H68" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
+    <row r="69" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
@@ -4189,8 +4155,8 @@
       </c>
       <c r="J69" s="5"/>
     </row>
-    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -4211,7 +4177,7 @@
       <c r="G70" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="2">
         <v>3.7</v>
       </c>
       <c r="I70" s="3" t="s">
@@ -4219,8 +4185,8 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="71" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
@@ -4241,7 +4207,7 @@
       <c r="G71" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="4">
         <v>4.5</v>
       </c>
       <c r="I71" s="5" t="s">
@@ -4249,8 +4215,8 @@
       </c>
       <c r="J71" s="5"/>
     </row>
-    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -4271,16 +4237,16 @@
       <c r="G72" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H72" s="2" t="n">
-        <v>4.4</v>
+      <c r="H72" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
+    <row r="73" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
@@ -4301,16 +4267,16 @@
       <c r="G73" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H73" s="4" t="n">
-        <v>4.9</v>
+      <c r="H73" s="4">
+        <v>4.9000000000000004</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J73" s="5"/>
     </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -4331,7 +4297,7 @@
       <c r="G74" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="2">
         <v>4.8</v>
       </c>
       <c r="I74" s="3" t="s">
@@ -4339,8 +4305,8 @@
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+    <row r="75" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
@@ -4361,7 +4327,7 @@
       <c r="G75" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="4">
         <v>3.7</v>
       </c>
       <c r="I75" s="5" t="s">
@@ -4369,8 +4335,8 @@
       </c>
       <c r="J75" s="5"/>
     </row>
-    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -4399,8 +4365,8 @@
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+    <row r="77" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
@@ -4421,7 +4387,7 @@
       <c r="G77" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="4">
         <v>3</v>
       </c>
       <c r="I77" s="5" t="s">
@@ -4429,8 +4395,8 @@
       </c>
       <c r="J77" s="5"/>
     </row>
-    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -4451,7 +4417,7 @@
       <c r="G78" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="2">
         <v>5</v>
       </c>
       <c r="I78" s="3" t="s">
@@ -4459,8 +4425,8 @@
       </c>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+    <row r="79" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
@@ -4481,7 +4447,7 @@
       <c r="G79" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="4">
         <v>5</v>
       </c>
       <c r="I79" s="5" t="s">
@@ -4489,8 +4455,8 @@
       </c>
       <c r="J79" s="5"/>
     </row>
-    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -4511,7 +4477,7 @@
       <c r="G80" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="2">
         <v>5</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -4519,8 +4485,8 @@
       </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+    <row r="81" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
@@ -4549,8 +4515,8 @@
       </c>
       <c r="J81" s="5"/>
     </row>
-    <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -4571,7 +4537,7 @@
       <c r="G82" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="2">
         <v>4.3</v>
       </c>
       <c r="I82" s="3" t="s">
@@ -4579,8 +4545,8 @@
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -4609,8 +4575,8 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -4639,8 +4605,8 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:10" ht="23" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -4669,8 +4635,8 @@
       </c>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="n">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -4699,8 +4665,8 @@
       </c>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="n">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -4729,8 +4695,8 @@
       </c>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="n">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -4759,8 +4725,8 @@
       </c>
       <c r="J88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="n">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -4789,8 +4755,8 @@
       </c>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="n">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -4819,8 +4785,8 @@
       </c>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="n">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -4849,8 +4815,8 @@
       </c>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="n">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -4879,8 +4845,8 @@
       </c>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="n">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -4909,8 +4875,8 @@
       </c>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="n">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -4939,8 +4905,8 @@
       </c>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="n">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -4969,8 +4935,8 @@
       </c>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="n">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -4999,8 +4965,8 @@
       </c>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="n">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -5029,8 +4995,8 @@
       </c>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="n">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -5059,8 +5025,8 @@
       </c>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="n">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -5089,8 +5055,8 @@
       </c>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="n">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
@@ -5119,8 +5085,8 @@
       </c>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="n">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -5149,8 +5115,8 @@
       </c>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="n">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -5179,8 +5145,8 @@
       </c>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="n">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -5209,8 +5175,8 @@
       </c>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="n">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -5239,8 +5205,8 @@
       </c>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="n">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -5269,8 +5235,8 @@
       </c>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="n">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
@@ -5299,8 +5265,8 @@
       </c>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="n">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
@@ -5329,8 +5295,8 @@
       </c>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="n">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
@@ -5359,8 +5325,8 @@
       </c>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="n">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -5389,8 +5355,8 @@
       </c>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="n">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
@@ -5419,8 +5385,8 @@
       </c>
       <c r="J110" s="3"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="n">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
@@ -5449,8 +5415,8 @@
       </c>
       <c r="J111" s="3"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="n">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
@@ -5480,36 +5446,32 @@
       <c r="J112" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{041818E2-A76C-48AB-BDF6-B49B45CBD29E}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{3458D5B6-621A-4E01-BDC1-2E2D46EA052F}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5541,8 +5503,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -5563,7 +5525,7 @@
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>4.2</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -5573,8 +5535,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -5595,7 +5557,7 @@
       <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="4">
         <v>4.5</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -5603,8 +5565,8 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -5625,16 +5587,16 @@
       <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>4.6</v>
+      <c r="H4" s="2">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -5663,8 +5625,8 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -5693,8 +5655,8 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -5715,7 +5677,7 @@
       <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="4">
         <v>4.2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -5723,8 +5685,8 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -5745,7 +5707,7 @@
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="2">
         <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -5753,8 +5715,8 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -5783,8 +5745,8 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -5805,7 +5767,7 @@
       <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2">
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -5813,8 +5775,8 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -5835,16 +5797,16 @@
       <c r="G11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>4.1</v>
+      <c r="H11" s="4">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -5865,7 +5827,7 @@
       <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="2">
         <v>3.5</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -5873,8 +5835,8 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -5895,7 +5857,7 @@
       <c r="G13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="4">
         <v>4</v>
       </c>
       <c r="I13" s="5" t="s">
@@ -5903,8 +5865,8 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -5925,7 +5887,7 @@
       <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="2">
         <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -5933,8 +5895,8 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -5955,7 +5917,7 @@
       <c r="G15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="4">
         <v>3.9</v>
       </c>
       <c r="I15" s="5" t="s">
@@ -5963,8 +5925,8 @@
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -5983,7 +5945,7 @@
       <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="2">
         <v>4.5</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -5991,8 +5953,8 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -6013,7 +5975,7 @@
       <c r="G17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="4">
         <v>4.5</v>
       </c>
       <c r="I17" s="5" t="s">
@@ -6021,8 +5983,8 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -6043,7 +6005,7 @@
       <c r="G18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="2">
         <v>4.7</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -6051,8 +6013,8 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -6081,8 +6043,8 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -6111,8 +6073,8 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -6133,7 +6095,7 @@
       <c r="G21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="4">
         <v>4.7</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -6141,8 +6103,8 @@
       </c>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -6163,7 +6125,7 @@
       <c r="G22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="2">
         <v>4</v>
       </c>
       <c r="I22" s="3" t="s">
@@ -6171,8 +6133,8 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -6193,7 +6155,7 @@
       <c r="G23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="4">
         <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -6201,8 +6163,8 @@
       </c>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -6231,8 +6193,8 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -6253,7 +6215,7 @@
       <c r="G25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4">
         <v>4.8</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -6261,8 +6223,8 @@
       </c>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -6291,8 +6253,8 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -6321,8 +6283,8 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -6352,36 +6314,28 @@
       <c r="J28" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J85"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6413,8 +6367,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -6435,7 +6389,7 @@
       <c r="G2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>4.3</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -6443,8 +6397,8 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6465,7 +6419,7 @@
       <c r="G3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="4">
         <v>3.9</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -6473,8 +6427,8 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -6495,7 +6449,7 @@
       <c r="G4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="2">
         <v>4.7</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -6503,8 +6457,8 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -6525,16 +6479,16 @@
       <c r="G5" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>4.9</v>
+      <c r="H5" s="4">
+        <v>4.9000000000000004</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -6555,16 +6509,16 @@
       <c r="G6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>4.4</v>
+      <c r="H6" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -6591,8 +6545,8 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -6613,7 +6567,7 @@
       <c r="G8" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="2">
         <v>4.5</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -6621,8 +6575,8 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -6643,7 +6597,7 @@
       <c r="G9" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="4">
         <v>4.8</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -6651,8 +6605,8 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -6673,7 +6627,7 @@
       <c r="G10" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2">
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -6681,8 +6635,8 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -6711,8 +6665,8 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -6733,16 +6687,16 @@
       <c r="G12" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>4.1</v>
+      <c r="H12" s="2">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -6763,7 +6717,7 @@
       <c r="G13" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="4">
         <v>5</v>
       </c>
       <c r="I13" s="5" t="s">
@@ -6771,8 +6725,8 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -6793,7 +6747,7 @@
       <c r="G14" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="2">
         <v>4.3</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -6801,8 +6755,8 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -6831,8 +6785,8 @@
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -6853,7 +6807,7 @@
       <c r="G16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="2">
         <v>5</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -6861,8 +6815,8 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -6891,8 +6845,8 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -6921,8 +6875,8 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -6943,7 +6897,7 @@
       <c r="G19" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="4">
         <v>4.5</v>
       </c>
       <c r="I19" s="5" t="s">
@@ -6951,8 +6905,8 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -6973,7 +6927,7 @@
       <c r="G20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="2">
         <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -6981,8 +6935,8 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -7003,7 +6957,7 @@
       <c r="G21" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="4">
         <v>4.5</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -7011,8 +6965,8 @@
       </c>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -7041,8 +6995,8 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -7063,7 +7017,7 @@
       <c r="G23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="4">
         <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -7071,8 +7025,8 @@
       </c>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -7093,7 +7047,7 @@
       <c r="G24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="2">
         <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -7101,8 +7055,8 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -7123,7 +7077,7 @@
       <c r="G25" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4">
         <v>4.2</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -7131,8 +7085,8 @@
       </c>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -7153,7 +7107,7 @@
       <c r="G26" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="2">
         <v>4.2</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -7161,8 +7115,8 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -7183,16 +7137,16 @@
       <c r="G27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>4.6</v>
+      <c r="H27" s="4">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -7213,16 +7167,16 @@
       <c r="G28" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>4.1</v>
+      <c r="H28" s="2">
+        <v>4.0999999999999996</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -7251,8 +7205,8 @@
       </c>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -7273,7 +7227,7 @@
       <c r="G30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="2">
         <v>4.2</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -7281,8 +7235,8 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -7309,8 +7263,8 @@
       </c>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -7331,7 +7285,7 @@
       <c r="G32" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="2">
         <v>4.5</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -7339,8 +7293,8 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -7361,7 +7315,7 @@
       <c r="G33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="4">
         <v>5</v>
       </c>
       <c r="I33" s="5" t="s">
@@ -7369,8 +7323,8 @@
       </c>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -7399,8 +7353,8 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -7421,7 +7375,7 @@
       <c r="G35" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="4">
         <v>5</v>
       </c>
       <c r="I35" s="5" t="s">
@@ -7429,8 +7383,8 @@
       </c>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -7451,16 +7405,16 @@
       <c r="G36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>4.6</v>
+      <c r="H36" s="2">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -7481,7 +7435,7 @@
       <c r="G37" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="4">
         <v>4.7</v>
       </c>
       <c r="I37" s="5" t="s">
@@ -7489,8 +7443,8 @@
       </c>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -7511,7 +7465,7 @@
       <c r="G38" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="2">
         <v>5</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -7519,8 +7473,8 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -7541,7 +7495,7 @@
       <c r="G39" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="4">
         <v>4.5</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -7549,8 +7503,8 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -7571,7 +7525,7 @@
       <c r="G40" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="2">
         <v>5</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -7579,8 +7533,8 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -7601,7 +7555,7 @@
       <c r="G41" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="4">
         <v>4</v>
       </c>
       <c r="I41" s="5" t="s">
@@ -7609,8 +7563,8 @@
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -7631,7 +7585,7 @@
       <c r="G42" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="2">
         <v>4.8</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -7639,8 +7593,8 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
@@ -7661,7 +7615,7 @@
       <c r="G43" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="4">
         <v>5</v>
       </c>
       <c r="I43" s="5" t="s">
@@ -7669,8 +7623,8 @@
       </c>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -7691,16 +7645,16 @@
       <c r="G44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H44" s="2" t="n">
-        <v>4.4</v>
+      <c r="H44" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -7729,8 +7683,8 @@
       </c>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -7751,7 +7705,7 @@
       <c r="G46" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="2">
         <v>3.7</v>
       </c>
       <c r="I46" s="3" t="s">
@@ -7759,8 +7713,8 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
@@ -7781,7 +7735,7 @@
       <c r="G47" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="4">
         <v>4.5</v>
       </c>
       <c r="I47" s="5" t="s">
@@ -7789,8 +7743,8 @@
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -7811,16 +7765,16 @@
       <c r="G48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>4.4</v>
+      <c r="H48" s="2">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
@@ -7841,16 +7795,16 @@
       <c r="G49" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>4.9</v>
+      <c r="H49" s="4">
+        <v>4.9000000000000004</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -7871,7 +7825,7 @@
       <c r="G50" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="2">
         <v>4.8</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -7879,8 +7833,8 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
@@ -7901,7 +7855,7 @@
       <c r="G51" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="4">
         <v>3.7</v>
       </c>
       <c r="I51" s="5" t="s">
@@ -7909,8 +7863,8 @@
       </c>
       <c r="J51" s="5"/>
     </row>
-    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -7939,8 +7893,8 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
@@ -7961,7 +7915,7 @@
       <c r="G53" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="4">
         <v>3</v>
       </c>
       <c r="I53" s="5" t="s">
@@ -7969,8 +7923,8 @@
       </c>
       <c r="J53" s="5"/>
     </row>
-    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -7991,7 +7945,7 @@
       <c r="G54" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="2">
         <v>5</v>
       </c>
       <c r="I54" s="3" t="s">
@@ -7999,8 +7953,8 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
@@ -8021,7 +7975,7 @@
       <c r="G55" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="4">
         <v>5</v>
       </c>
       <c r="I55" s="5" t="s">
@@ -8029,8 +7983,8 @@
       </c>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -8051,7 +8005,7 @@
       <c r="G56" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="2">
         <v>5</v>
       </c>
       <c r="I56" s="3" t="s">
@@ -8059,8 +8013,8 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
@@ -8089,8 +8043,8 @@
       </c>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -8111,7 +8065,7 @@
       <c r="G58" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="2">
         <v>4.3</v>
       </c>
       <c r="I58" s="3" t="s">
@@ -8119,8 +8073,8 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -8149,8 +8103,8 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -8179,8 +8133,8 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:10" ht="23" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -8209,8 +8163,8 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -8239,8 +8193,8 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="n">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -8269,8 +8223,8 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -8299,8 +8253,8 @@
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="n">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -8329,8 +8283,8 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -8359,8 +8313,8 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="n">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -8389,8 +8343,8 @@
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -8419,8 +8373,8 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="n">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -8449,8 +8403,8 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -8479,8 +8433,8 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="n">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -8509,8 +8463,8 @@
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -8539,8 +8493,8 @@
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="n">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -8569,8 +8523,8 @@
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -8599,8 +8553,8 @@
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="n">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -8629,8 +8583,8 @@
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -8659,8 +8613,8 @@
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="n">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -8689,8 +8643,8 @@
       </c>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -8719,8 +8673,8 @@
       </c>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="n">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -8749,8 +8703,8 @@
       </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -8779,8 +8733,8 @@
       </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="n">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -8809,8 +8763,8 @@
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -8839,8 +8793,8 @@
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -8869,8 +8823,8 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -8899,8 +8853,8 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -8930,148 +8884,135 @@
       <c r="J85" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>493</v>
       </c>
       <c r="B1" s="9"/>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>494</v>
       </c>
       <c r="B2" s="9"/>
     </row>
-    <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>495</v>
       </c>
       <c r="B4" s="12"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Active Deal 🤝")</f>
+      <c r="B5" s="14">
+        <f>COUNTIF('All Leads'!I:I,"Active Deal 🤝")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Replied 💬")</f>
+      <c r="B6" s="16">
+        <f>COUNTIF('All Leads'!I:I,"Replied 💬")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="B7" s="14" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Sent 📤")</f>
+      <c r="B7" s="14">
+        <f>COUNTIF('All Leads'!I:I,"Sent 📤")</f>
         <v>39</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Draft Ready 📝")</f>
+      <c r="B8" s="16">
+        <f>COUNTIF('All Leads'!I:I,"Draft Ready 📝")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="B9" s="14" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Not Contacted")</f>
+      <c r="B9" s="14">
+        <f>COUNTIF('All Leads'!I:I,"Not Contacted")</f>
         <v>69</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>501</v>
       </c>
-      <c r="B10" s="18" t="n">
-        <f aca="false">COUNTA('All Leads'!A:A)-1</f>
+      <c r="B10" s="18">
+        <f>COUNTA('All Leads'!A:A)-1</f>
         <v>111</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="B11" s="20" t="n">
-        <f aca="false">COUNTIF('All Leads'!I:I,"Active Deal 🤝")+COUNTIF('All Leads'!I:I,"Replied 💬")+COUNTIF('All Leads'!I:I,"Sent 📤")+COUNTIF('All Leads'!I:I,"Draft Ready 📝")</f>
+      <c r="B11" s="20">
+        <f>COUNTIF('All Leads'!I:I,"Active Deal 🤝")+COUNTIF('All Leads'!I:I,"Replied 💬")+COUNTIF('All Leads'!I:I,"Sent 📤")+COUNTIF('All Leads'!I:I,"Draft Ready 📝")</f>
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>503</v>
       </c>
       <c r="B13" s="12"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="14" t="n">
-        <f aca="false">COUNTIF('All Leads'!G:G,"Kitwe")</f>
+      <c r="B14" s="14">
+        <f>COUNTIF('All Leads'!G:G,"Kitwe")</f>
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIF('All Leads'!G:G,"Lusaka")</f>
+      <c r="B15" s="16">
+        <f>COUNTIF('All Leads'!G:G,"Lusaka")</f>
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>